--- a/results/03_stylised_facts.xlsx
+++ b/results/03_stylised_facts.xlsx
@@ -1463,7 +1463,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Not significant</t>
+          <t>Inconclusive (GARCH at boundary)</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Supported</t>
+          <t>Inconclusive (GARCH at boundary)</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Not significant</t>
+          <t>Inconclusive (GARCH at boundary)</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Supported</t>
+          <t>Inconclusive (GARCH at boundary)</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6460,6 +6460,16 @@
           <t>Quantile 99%</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Bootstrap p centred (sensitivity)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Bootstrap p two-sided (sensitivity)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -6498,6 +6508,12 @@
       </c>
       <c r="K2" t="n">
         <v>0.03169501834639981</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.545</v>
       </c>
     </row>
     <row r="3">
@@ -6534,6 +6550,12 @@
       <c r="K3" t="n">
         <v>0.07668322868978676</v>
       </c>
+      <c r="L3" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.053</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n"/>
@@ -6569,6 +6591,12 @@
       <c r="K4" t="n">
         <v>0.1207657067668586</v>
       </c>
+      <c r="L4" t="n">
+        <v>0.0395</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.166</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -6607,6 +6635,12 @@
       </c>
       <c r="K5" t="n">
         <v>0.02605884237265368</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.226</v>
       </c>
     </row>
     <row r="6">
@@ -6643,6 +6677,12 @@
       <c r="K6" t="n">
         <v>0.05693710518121</v>
       </c>
+      <c r="L6" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.057</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -6677,6 +6717,12 @@
       </c>
       <c r="K7" t="n">
         <v>0.1032643850572533</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
